--- a/public/templates/finance-import/finance2.xlsx
+++ b/public/templates/finance-import/finance2.xlsx
@@ -1,65 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\hydr-sales-leads-tracker\templates\finance-import\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074F59E7-2EE1-4AF4-B3DB-CA9BA60FBC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Company" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Income</t>
-  </si>
-  <si>
-    <t>Expense</t>
-  </si>
-  <si>
-    <t>Deadline</t>
-  </si>
-  <si>
-    <t>Sofia District Heating H2 Blend</t>
-  </si>
-  <si>
-    <t>FAT</t>
-  </si>
-  <si>
-    <t>SAT</t>
-  </si>
-  <si>
-    <t>Istanbul Steel Annealing Line</t>
-  </si>
-  <si>
-    <t>Engineering done</t>
-  </si>
-  <si>
-    <t>Commissioned</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="2">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -89,22 +67,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -429,171 +399,165 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Project</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Income</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Deadline</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Category</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Sofia District Heating H2 Blend</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46037.0000462963</v>
+      </c>
+      <c r="C2">
+        <v>50000</v>
+      </c>
+      <c r="D2">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1">
-        <v>46068</v>
-      </c>
-      <c r="C2">
-        <v>500000</v>
-      </c>
-      <c r="D2">
-        <v>45000</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
+      <c r="E2" t="str">
+        <v>Prepayment</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Sofia District Heating H2 Blend</v>
       </c>
       <c r="B3" s="1">
-        <v>46096</v>
+        <v>46063.0000462963</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>45000</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
+        <v>12000</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Component costs</v>
+      </c>
+      <c r="F3" t="str">
+        <v>materials</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Sofia District Heating H2 Blend</v>
       </c>
       <c r="B4" s="1">
-        <v>46127</v>
+        <v>46082.0000462963</v>
       </c>
       <c r="C4">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>48000</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
+        <v>8000</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Man-hrs</v>
+      </c>
+      <c r="F4" t="str">
+        <v>man-hr</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Sofia District Heating H2 Blend</v>
       </c>
       <c r="B5" s="1">
-        <v>46157</v>
+        <v>46132.0000462963</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
+        <v>5000</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Installation</v>
+      </c>
+      <c r="F5" t="str">
+        <v>installation</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Month</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Other</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-01</v>
+      </c>
+      <c r="B2">
         <v>45000</v>
       </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1">
-        <v>46188</v>
-      </c>
-      <c r="C6">
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D6">
+      <c r="D2" t="str">
+        <v>actual</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-02</v>
+      </c>
+      <c r="B3">
         <v>45000</v>
       </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
-        <v>46218</v>
-      </c>
-      <c r="C7">
-        <v>120000</v>
-      </c>
-      <c r="D7">
-        <v>52000</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>46244</v>
-      </c>
-      <c r="C8">
-        <v>400000</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1">
-        <v>46260</v>
-      </c>
-      <c r="C9">
-        <v>200000</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
+      <c r="C3">
+        <v>1200</v>
+      </c>
+      <c r="D3" t="str">
+        <v>projected</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C1:E8 A1 A8 A2 A3 A4 A5 A6 A7" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>